--- a/giro_da_praça_ofertas - SAB - DOM.xlsx
+++ b/giro_da_praça_ofertas - SAB - DOM.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -484,7 +520,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1698,801 +1734,393 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>302070</v>
+        <v>289789</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA MISTA BEATS 269ML GIN E FRUTAS TROPICAIS</t>
+          <t>COXA DE FRANGO SEARA BDJ 1KG</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="6" t="n">
-        <v>8.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>161871</v>
+        <v>289786</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>REFRIGANTE TUCHAUA 2L GUARANA</t>
+          <t>COXINHA DA ASA DE FRANGO SEARA PCT 1KG</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="6" t="n">
-        <v>8.19</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>104406</v>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="n">
-        <v>11.49</v>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>119927</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="10" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>104404</v>
+        <v>298984</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE FANTA 2L LARANJA</t>
+          <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="6" t="n">
-        <v>10.49</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>102282</v>
+        <v>289794</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="6" t="n">
-        <v>8.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>184034</v>
+        <v>291441</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA HEINEKEN 250ML LAGER LONG NECK LAGER </t>
+          <t>SOBRECOXA DE FRANGO SEARA PCT 1KG</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="n">
-        <v>5.39</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>157496</v>
+        <v>314513</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 600ML</t>
+          <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="6" t="n">
-        <v>13.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>239446</v>
+        <v>330507</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 269ML LAGER</t>
+          <t>LINGUIÇA NUTRIBRAS 350G CALABRESA</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="6" t="n">
-        <v>3.19</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>287369</v>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="n">
-        <v>3.79</v>
-      </c>
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>170451</v>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CERVEJA BRAHMA 15 X 269ML CHOPP </t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="6" t="n">
-        <v>3.29</v>
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="10" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>271001</v>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>CERVEJA IMPERIO 15 X 269ML PURO MALTE</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="6" t="n">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr"/>
+      <c r="F63" s="10" t="n">
         <v>2.99</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>324556</v>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="6" t="n">
-        <v>3.09</v>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>104903</v>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>BATATA DOCE KG ROSA</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr"/>
+      <c r="F64" s="10" t="n">
+        <v>5.29</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>172548</v>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>AGUARDENTE VELHO BARREIRO 910ML GOLD OURO</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="6" t="n">
-        <v>25.99</v>
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>105010</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="10" t="n">
+        <v>5.49</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>107799</v>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>BEBIDA RAIZES AMARGAS DA RAÇA 880ML</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="6" t="n">
-        <v>11.99</v>
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr"/>
+      <c r="F66" s="10" t="n">
+        <v>4.69</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>192492</v>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>BITTER APEROL 750ML</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="n">
-        <v>75.98999999999999</v>
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>104863</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>TOMATE SALADETE KG</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr"/>
+      <c r="F67" s="10" t="n">
+        <v>5.99</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>102085</v>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>CACHAÇA 51 965ML</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="6" t="n">
-        <v>13.99</v>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>104919</v>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>CEBOLA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr"/>
+      <c r="F68" s="10" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>215568</v>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>CACHAÇA BANANAZINHA 900ML</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="6" t="n">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>301843</v>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>CAMPARI 998ML</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="6" t="n">
-        <v>85.98999999999999</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>102186</v>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>CONHAQUE PRESIDENTE 900ML</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>102093</v>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>VODKA ORLOFF 1L CRISTAL</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="6" t="n">
-        <v>48.99</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>201454</v>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>WHISKY BALLANTINES 750ML FINEST 8 ANOS</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr"/>
-      <c r="F73" s="6" t="n">
-        <v>94.98999999999999</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>109726</v>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WHISKY BUCHANANS 1L 12 ANOS </t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="6" t="n">
-        <v>279.99</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>102071</v>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>WHISKY J&amp;B 1L 8 ANOS RARE</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr"/>
-      <c r="F75" s="6" t="n">
-        <v>99.98999999999999</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>137381</v>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>WHISKY JOHNNIE WALKER 1L RED LABEL</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="6" t="n">
-        <v>145.99</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>248750</v>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="6" t="n">
-        <v>75.98999999999999</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITAO 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>102036</v>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr"/>
-      <c r="F78" s="6" t="n">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>289789</v>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>COXA DE FRANGO SEARA BDJ 1KG</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="6" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>289786</v>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>COXINHA DA ASA DE FRANGO SEARA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="6" t="n">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>298984</v>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="6" t="n">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>289794</v>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="6" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>291441</v>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>SOBRECOXA DE FRANGO SEARA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="6" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>314513</v>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr"/>
-      <c r="F85" s="6" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>330507</v>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>LINGUIÇA NUTRIBRAS 350G CALABRESA</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="6" t="n">
-        <v>9.99</v>
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>104992</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr"/>
+      <c r="F69" s="10" t="n">
+        <v>3.49</v>
       </c>
     </row>
   </sheetData>

--- a/giro_da_praça_ofertas - SAB - DOM.xlsx
+++ b/giro_da_praça_ofertas - SAB - DOM.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1780,26 +1780,26 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - PERECIVEIS 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C55" s="3" t="n">
         <v>119927</v>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr"/>
-      <c r="F55" s="10" t="n">
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="6" t="n">
         <v>12.99</v>
       </c>
     </row>
@@ -1943,183 +1943,207 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>104931</v>
+        <v>104864</v>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>ABACATE KG</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr"/>
       <c r="F62" s="10" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="6" t="n">
         <v>4.49</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C64" s="3" t="n">
         <v>104947</v>
       </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="10" t="n">
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="6" t="n">
         <v>2.99</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C64" s="8" t="n">
+      <c r="C65" s="3" t="n">
         <v>104903</v>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>BATATA DOCE KG ROSA</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="10" t="n">
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="6" t="n">
         <v>5.29</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C66" s="3" t="n">
         <v>105010</v>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>BATATA MONALISA KG</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="10" t="n">
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="6" t="n">
         <v>5.49</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C66" s="8" t="n">
+      <c r="C67" s="3" t="n">
         <v>105001</v>
       </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>BETERRABA KG</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="10" t="n">
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="6" t="n">
         <v>4.69</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
-      <c r="C67" s="8" t="n">
+      <c r="C68" s="3" t="n">
         <v>104863</v>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>TOMATE SALADETE KG</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="10" t="n">
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="6" t="n">
         <v>5.99</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
         </is>
       </c>
-      <c r="C68" s="8" t="n">
+      <c r="C69" s="3" t="n">
         <v>104919</v>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr"/>
-      <c r="F68" s="10" t="n">
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="6" t="n">
         <v>1.99</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>SABADO/DOMINGO - HORTI 29 E 30/11/25</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C69" s="8" t="n">
+      <c r="C70" s="3" t="n">
         <v>104992</v>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr"/>
-      <c r="F69" s="10" t="n">
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="6" t="n">
         <v>3.49</v>
       </c>
     </row>
